--- a/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>FOTB</t>
   </si>
@@ -663,11 +663,12 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -693,22 +694,22 @@
         <v>45199</v>
       </c>
       <c r="E7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44561</v>
       </c>
       <c r="K7" s="2">
         <v>44469</v>
@@ -734,22 +735,22 @@
         <v>21700</v>
       </c>
       <c r="E8" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F8" s="3">
         <v>18000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9700</v>
-      </c>
-      <c r="J8" s="3">
-        <v>10100</v>
       </c>
       <c r="K8" s="3">
         <v>10600</v>
@@ -1052,22 +1053,22 @@
         <v>10000</v>
       </c>
       <c r="E17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F17" s="3">
         <v>7500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1500</v>
       </c>
       <c r="K17" s="3">
         <v>1600</v>
@@ -1093,22 +1094,22 @@
         <v>11700</v>
       </c>
       <c r="E18" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F18" s="3">
         <v>10500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>8600</v>
       </c>
       <c r="K18" s="3">
         <v>9100</v>
@@ -1151,22 +1152,22 @@
         <v>-6500</v>
       </c>
       <c r="E20" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-5400</v>
       </c>
       <c r="K20" s="3">
         <v>-4000</v>
@@ -1274,22 +1275,22 @@
         <v>5100</v>
       </c>
       <c r="E23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F23" s="3">
         <v>4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>3200</v>
       </c>
       <c r="K23" s="3">
         <v>5100</v>
@@ -1315,22 +1316,22 @@
         <v>1400</v>
       </c>
       <c r="E24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1400</v>
       </c>
       <c r="H24" s="3">
         <v>1400</v>
       </c>
       <c r="I24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J24" s="3">
         <v>700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>800</v>
       </c>
       <c r="K24" s="3">
         <v>1400</v>
@@ -1397,22 +1398,22 @@
         <v>3700</v>
       </c>
       <c r="E26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>2300</v>
       </c>
       <c r="K26" s="3">
         <v>3700</v>
@@ -1438,22 +1439,22 @@
         <v>3700</v>
       </c>
       <c r="E27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>2300</v>
       </c>
       <c r="K27" s="3">
         <v>3700</v>
@@ -1643,22 +1644,22 @@
         <v>6500</v>
       </c>
       <c r="E32" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F32" s="3">
         <v>6500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>5400</v>
       </c>
       <c r="K32" s="3">
         <v>4000</v>
@@ -1684,22 +1685,22 @@
         <v>3700</v>
       </c>
       <c r="E33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>2300</v>
       </c>
       <c r="K33" s="3">
         <v>3700</v>
@@ -1766,22 +1767,22 @@
         <v>3700</v>
       </c>
       <c r="E35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>2300</v>
       </c>
       <c r="K35" s="3">
         <v>3700</v>
@@ -1812,22 +1813,22 @@
         <v>45199</v>
       </c>
       <c r="E38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44561</v>
       </c>
       <c r="K38" s="2">
         <v>44469</v>
@@ -1887,22 +1888,22 @@
         <v>4500</v>
       </c>
       <c r="E41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F41" s="3">
         <v>52500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>8200</v>
       </c>
       <c r="K41" s="3">
         <v>7200</v>
@@ -1928,22 +1929,22 @@
         <v>38700</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>49100</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>45200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>30600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>76600</v>
@@ -2174,22 +2175,22 @@
         <v>14100</v>
       </c>
       <c r="E48" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F48" s="3">
         <v>14500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>14600</v>
       </c>
       <c r="H48" s="3">
         <v>14600</v>
       </c>
       <c r="I48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J48" s="3">
         <v>14400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>9800</v>
       </c>
       <c r="K48" s="3">
         <v>9800</v>
@@ -2217,20 +2218,20 @@
       <c r="E49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3">
         <v>2400</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J49" s="3">
-        <v>2400</v>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -2420,22 +2421,22 @@
         <v>1456800</v>
       </c>
       <c r="E54" s="3">
+        <v>1455100</v>
+      </c>
+      <c r="F54" s="3">
         <v>1353500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1354700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1265100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1161600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1077800</v>
-      </c>
-      <c r="J54" s="3">
-        <v>970900</v>
       </c>
       <c r="K54" s="3">
         <v>993500</v>
@@ -2659,19 +2660,19 @@
         <v>118500</v>
       </c>
       <c r="E61" s="3">
+        <v>139000</v>
+      </c>
+      <c r="F61" s="3">
         <v>161000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>189800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>181300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>91300</v>
-      </c>
-      <c r="I61" s="3">
-        <v>58500</v>
       </c>
       <c r="J61" s="3">
         <v>58500</v>
@@ -2864,22 +2865,22 @@
         <v>1377100</v>
       </c>
       <c r="E66" s="3">
+        <v>1376900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1276500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1283200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1196400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1095200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1013600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>907200</v>
       </c>
       <c r="K66" s="3">
         <v>931300</v>
@@ -3088,20 +3089,20 @@
       <c r="E72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3">
         <v>60200</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J72" s="3">
-        <v>49300</v>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
@@ -3250,22 +3251,22 @@
         <v>79700</v>
       </c>
       <c r="E76" s="3">
+        <v>78200</v>
+      </c>
+      <c r="F76" s="3">
         <v>77000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>71500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>68700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>64200</v>
-      </c>
-      <c r="J76" s="3">
-        <v>63700</v>
       </c>
       <c r="K76" s="3">
         <v>62100</v>
@@ -3337,22 +3338,22 @@
         <v>45199</v>
       </c>
       <c r="E80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44561</v>
       </c>
       <c r="K80" s="2">
         <v>44469</v>
@@ -3378,22 +3379,22 @@
         <v>3700</v>
       </c>
       <c r="E81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>2300</v>
       </c>
       <c r="K81" s="3">
         <v>3700</v>

--- a/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>FOTB</t>
   </si>
@@ -656,119 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>40816</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E8" s="3">
         <v>21700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9400</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2700</v>
       </c>
       <c r="O8" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -808,8 +814,11 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -849,8 +858,11 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -866,8 +878,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,8 +920,11 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,8 +964,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -989,8 +1008,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1024,14 +1046,17 @@
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,34 +1069,35 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E17" s="3">
         <v>10000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1400</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1600</v>
       </c>
       <c r="L17" s="3">
         <v>1600</v>
@@ -1080,54 +1106,60 @@
         <v>1600</v>
       </c>
       <c r="N17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E18" s="3">
         <v>11700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1143,49 +1175,53 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1219,14 +1255,17 @@
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1266,90 +1305,99 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>5100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1400</v>
       </c>
       <c r="I24" s="3">
         <v>1400</v>
       </c>
       <c r="J24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1389,90 +1437,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E26" s="3">
         <v>3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E27" s="3">
         <v>3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1512,8 +1569,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1553,8 +1613,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1594,8 +1657,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1635,90 +1701,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E32" s="3">
         <v>6500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E33" s="3">
         <v>3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1758,95 +1833,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E35" s="3">
         <v>3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>40816</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1862,8 +1946,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1879,90 +1964,97 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E42" s="3">
         <v>38700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>49100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>45200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>30600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>31500</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>76600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>53500</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2002,8 +2094,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2043,8 +2138,11 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2084,8 +2182,11 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2125,8 +2226,11 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2166,54 +2270,60 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E48" s="3">
         <v>14100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>14600</v>
       </c>
       <c r="I48" s="3">
         <v>14600</v>
       </c>
       <c r="J48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K48" s="3">
         <v>14400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
+      <c r="D49" s="3">
+        <v>2400</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>5</v>
@@ -2221,12 +2331,12 @@
       <c r="F49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3">
         <v>2400</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2242,14 +2352,17 @@
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2289,8 +2402,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2330,8 +2446,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2371,8 +2490,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2412,49 +2534,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1488900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1456800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1455100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1353500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1354700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1265100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1161600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1077800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>993500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>958700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2470,8 +2598,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2487,8 +2616,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2528,8 +2658,11 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2569,8 +2702,11 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2610,8 +2746,11 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2651,49 +2790,55 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>153500</v>
+      </c>
+      <c r="E61" s="3">
         <v>118500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>139000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>161000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>189800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>181300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>91300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>58500</v>
       </c>
       <c r="K61" s="3">
         <v>58500</v>
       </c>
       <c r="L61" s="3">
+        <v>58500</v>
+      </c>
+      <c r="M61" s="3">
         <v>63500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2733,8 +2878,11 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2774,8 +2922,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2815,8 +2966,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2856,49 +3010,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1402300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1377100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1376900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1276500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1283200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1196400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1095200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1013600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>931300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>900400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2914,8 +3074,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2955,8 +3116,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2996,8 +3160,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3037,8 +3204,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3078,13 +3248,16 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>73300</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>5</v>
@@ -3092,12 +3265,12 @@
       <c r="F72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3">
         <v>60200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3113,14 +3286,17 @@
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
+      <c r="N72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3160,8 +3336,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3201,8 +3380,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3242,49 +3424,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E76" s="3">
         <v>79700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>78200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>77000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>71500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>68700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>66400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>64200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3324,95 +3512,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>40816</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E81" s="3">
         <v>3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3428,8 +3625,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3463,14 +3661,17 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3510,8 +3711,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3755,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3592,8 +3799,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3633,8 +3843,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3674,8 +3887,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3709,14 +3925,17 @@
       <c r="M89" s="3">
         <v>0</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3732,8 +3951,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3767,14 +3987,17 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3814,8 +4037,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3855,8 +4081,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3890,14 +4119,17 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3913,8 +4145,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3954,8 +4187,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3995,8 +4231,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4036,8 +4275,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4077,8 +4319,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4112,14 +4357,17 @@
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4159,8 +4407,11 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4194,10 +4445,13 @@
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
   <si>
     <t>FOTB</t>
   </si>
@@ -656,125 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>40816</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F8" s="3">
         <v>22700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>21700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>19900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>18000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>16500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>14300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>11400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -817,8 +831,14 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +881,14 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,8 +905,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -923,8 +951,14 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,8 +1001,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1011,31 +1051,37 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -1049,14 +1095,20 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,96 +1122,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F17" s="3">
         <v>11100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>7500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1600</v>
       </c>
       <c r="N17" s="3">
         <v>1600</v>
       </c>
       <c r="O17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F18" s="3">
         <v>11600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>11700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>10700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>10500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>10900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>11300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>9700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>8200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,52 +1242,60 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-5700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-6600</v>
       </c>
       <c r="G20" s="3">
         <v>-6500</v>
       </c>
       <c r="H20" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-7200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-4500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1258,14 +1332,20 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1308,96 +1388,114 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F23" s="3">
         <v>5900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>5100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>4200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>700</v>
       </c>
       <c r="L24" s="3">
         <v>1400</v>
       </c>
       <c r="M24" s="3">
+        <v>700</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,96 +1538,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F26" s="3">
         <v>4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1900</v>
       </c>
       <c r="L26" s="3">
         <v>3700</v>
       </c>
       <c r="M26" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N26" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F27" s="3">
         <v>4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1900</v>
       </c>
       <c r="L27" s="3">
         <v>3700</v>
       </c>
       <c r="M27" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N27" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O27" s="3">
         <v>2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1688,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1738,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1788,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,96 +1838,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F32" s="3">
         <v>5700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>6500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>6600</v>
       </c>
       <c r="G32" s="3">
         <v>6500</v>
       </c>
       <c r="H32" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J32" s="3">
         <v>7200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>4500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F33" s="3">
         <v>4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1900</v>
       </c>
       <c r="L33" s="3">
         <v>3700</v>
       </c>
       <c r="M33" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N33" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O33" s="3">
         <v>2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,101 +1988,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F35" s="3">
         <v>4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1900</v>
       </c>
       <c r="L35" s="3">
         <v>3700</v>
       </c>
       <c r="M35" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N35" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O35" s="3">
         <v>2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>40816</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2117,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,96 +2137,110 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5100</v>
+        <v>3500</v>
       </c>
       <c r="E41" s="3">
         <v>4500</v>
       </c>
       <c r="F41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="H41" s="3">
         <v>4600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>52500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>46300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F42" s="3">
         <v>22600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>38700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>49100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>45200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>30600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>31500</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>76600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>53500</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2097,8 +2283,14 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2141,8 +2333,14 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2185,8 +2383,14 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2229,8 +2433,14 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2273,76 +2483,88 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F48" s="3">
         <v>9900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>14100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>10400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>14600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>14600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>14400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>9900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3">
         <v>2400</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3">
         <v>2400</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2355,14 +2577,20 @@
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2633,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,8 +2683,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2493,8 +2733,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,52 +2783,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1626200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1546300</v>
+      </c>
+      <c r="F54" s="3">
         <v>1488900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1456800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1455100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1353500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1354700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1265100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1161600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1077800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>993500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>958700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2857,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,8 +2877,10 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2661,8 +2923,14 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2705,8 +2973,14 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2749,8 +3023,14 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2793,52 +3073,64 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>84500</v>
+      </c>
+      <c r="F61" s="3">
         <v>153500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>118500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>139000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>161000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>189800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>181300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>91300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>58500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>58500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>63500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2881,8 +3173,14 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3223,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3273,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,52 +3323,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1532100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1455300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1402300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1377100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1376900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1276500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1283200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1196400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1095200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1013600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>931300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>900400</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3397,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3443,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3493,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3543,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,32 +3593,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>73300</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>60200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3289,14 +3637,20 @@
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3693,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3743,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,52 +3793,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>91000</v>
+      </c>
+      <c r="F76" s="3">
         <v>86600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>79700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>78200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>77000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>71500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>68700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>66400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>64200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>62100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>58300</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,101 +3893,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>40816</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F81" s="3">
         <v>4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1900</v>
       </c>
       <c r="L81" s="3">
         <v>3700</v>
       </c>
       <c r="M81" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N81" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O81" s="3">
         <v>2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,8 +4022,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3664,14 +4062,20 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +4118,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +4168,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4218,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4268,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,8 +4318,14 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3928,14 +4362,20 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,8 +4392,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3990,14 +4432,20 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4488,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,8 +4538,14 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4122,14 +4582,20 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4612,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4190,8 +4658,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4708,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4758,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,8 +4808,14 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4360,14 +4852,20 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4410,8 +4908,14 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4448,10 +4952,16 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3" t="s">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>FOTB</t>
   </si>
@@ -656,139 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40816</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>24600</v>
+        <v>15600</v>
       </c>
       <c r="E8" s="3">
-        <v>23300</v>
+        <v>13300</v>
       </c>
       <c r="F8" s="3">
-        <v>22700</v>
+        <v>12800</v>
       </c>
       <c r="G8" s="3">
-        <v>21700</v>
+        <v>13000</v>
       </c>
       <c r="H8" s="3">
-        <v>19900</v>
+        <v>13000</v>
       </c>
       <c r="I8" s="3">
-        <v>18000</v>
+        <v>11800</v>
       </c>
       <c r="J8" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K8" s="3">
         <v>16500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9400</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>2700</v>
       </c>
       <c r="R8" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -837,31 +844,34 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>11600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -887,8 +897,11 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,8 +920,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -957,8 +971,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1007,31 +1024,34 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1057,34 +1077,37 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+        <v>500</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
@@ -1101,14 +1124,17 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,43 +1150,44 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12800</v>
+        <v>7200</v>
       </c>
       <c r="E17" s="3">
-        <v>11800</v>
+        <v>7600</v>
       </c>
       <c r="F17" s="3">
-        <v>11100</v>
+        <v>7400</v>
       </c>
       <c r="G17" s="3">
-        <v>10000</v>
+        <v>5400</v>
       </c>
       <c r="H17" s="3">
-        <v>9200</v>
+        <v>7900</v>
       </c>
       <c r="I17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J17" s="3">
         <v>7500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1600</v>
       </c>
       <c r="O17" s="3">
         <v>1600</v>
@@ -1169,63 +1196,69 @@
         <v>1600</v>
       </c>
       <c r="Q17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11800</v>
+        <v>8400</v>
       </c>
       <c r="E18" s="3">
-        <v>11500</v>
+        <v>5700</v>
       </c>
       <c r="F18" s="3">
-        <v>11600</v>
+        <v>5300</v>
       </c>
       <c r="G18" s="3">
-        <v>11700</v>
+        <v>7600</v>
       </c>
       <c r="H18" s="3">
-        <v>10700</v>
+        <v>5100</v>
       </c>
       <c r="I18" s="3">
-        <v>10500</v>
+        <v>4600</v>
       </c>
       <c r="J18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K18" s="3">
         <v>10900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,81 +1277,85 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6600</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>-6700</v>
+        <v>500</v>
       </c>
       <c r="F20" s="3">
+        <v>500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N20" s="3">
         <v>-5700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>4500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1338,37 +1375,40 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>1200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1394,108 +1434,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E23" s="3">
         <v>5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1400</v>
       </c>
       <c r="L24" s="3">
         <v>1400</v>
       </c>
       <c r="M24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1593,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E26" s="3">
         <v>3800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E27" s="3">
         <v>3800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1752,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1744,8 +1805,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1858,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,108 +1911,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6600</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>6700</v>
+        <v>-500</v>
       </c>
       <c r="F32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>7200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N32" s="3">
         <v>5700</v>
       </c>
-      <c r="G32" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>6600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>7200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>4700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>5700</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E33" s="3">
         <v>3800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2070,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E35" s="3">
         <v>3800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40816</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2204,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,131 +2225,138 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3500</v>
+        <v>38800</v>
       </c>
       <c r="E41" s="3">
-        <v>4500</v>
+        <v>42200</v>
       </c>
       <c r="F41" s="3">
-        <v>5100</v>
+        <v>27500</v>
       </c>
       <c r="G41" s="3">
-        <v>4500</v>
+        <v>27600</v>
       </c>
       <c r="H41" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I41" s="3">
+        <v>43200</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3">
         <v>52500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>38700</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>22600</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>38700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>49100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>45200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>30600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>31500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>76600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>53500</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2289,31 +2382,34 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2339,31 +2435,34 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>28300</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>28200</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
+        <v>59000</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>49300</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2389,31 +2488,34 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>73700</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>55900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>32900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
-        <v>0</v>
+        <v>121000</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>102100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2439,31 +2541,34 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>184200</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>172900</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>167000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>165700</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
+        <v>145300</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>124200</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2489,85 +2594,91 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E48" s="3">
         <v>9500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13400</v>
       </c>
-      <c r="F48" s="3">
-        <v>9900</v>
-      </c>
       <c r="G48" s="3">
+        <v>13800</v>
+      </c>
+      <c r="H48" s="3">
         <v>14100</v>
       </c>
-      <c r="H48" s="3">
-        <v>14300</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>14500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>14600</v>
       </c>
       <c r="L48" s="3">
         <v>14600</v>
       </c>
       <c r="M48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="N48" s="3">
         <v>14400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>5</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>2400</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2583,14 +2694,17 @@
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2753,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,31 +2806,34 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>33400</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>33100</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>32800</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>41200</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2739,8 +2859,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,58 +2912,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1672400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1626200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1546300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1488900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1456800</v>
       </c>
-      <c r="H54" s="3">
-        <v>1455100</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3">
         <v>1353500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1354700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1265100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1161600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1077800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>993500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>958700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +2988,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,31 +3009,32 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1481800</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>1437800</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>1354300</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>1235700</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
+        <v>1244400</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1101300</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2929,8 +3060,11 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2944,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2979,31 +3113,34 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -3029,31 +3166,34 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1481800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1437800</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1354300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1337700</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
+        <v>1244400</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1101300</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3079,81 +3219,87 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E61" s="3">
         <v>80500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>84500</v>
       </c>
-      <c r="F61" s="3">
-        <v>153500</v>
-      </c>
       <c r="G61" s="3">
+        <v>55300</v>
+      </c>
+      <c r="H61" s="3">
         <v>118500</v>
       </c>
-      <c r="H61" s="3">
-        <v>139000</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>161000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>189800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>181300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>91300</v>
-      </c>
-      <c r="M61" s="3">
-        <v>58500</v>
       </c>
       <c r="N61" s="3">
         <v>58500</v>
       </c>
       <c r="O61" s="3">
+        <v>58500</v>
+      </c>
+      <c r="P61" s="3">
         <v>63500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>13800</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
+        <v>14200</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>14200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3179,8 +3325,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3378,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3431,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,58 +3484,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1569700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1532100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1455300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1402300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1377100</v>
       </c>
-      <c r="H66" s="3">
-        <v>1376900</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>1276500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1283200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1196400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1095200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1013600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>931300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>900400</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3560,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3611,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3664,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3717,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,8 +3770,11 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3610,24 +3784,24 @@
       <c r="E72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3">
         <v>73300</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>60200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3643,14 +3817,17 @@
       <c r="P72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +3876,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +3929,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,58 +3982,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102700</v>
+      </c>
+      <c r="E76" s="3">
         <v>94200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>91000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>86600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>79700</v>
       </c>
-      <c r="H76" s="3">
-        <v>78200</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3">
         <v>77000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>68700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>66400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>64200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>62100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4088,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40816</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E81" s="3">
         <v>3800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,31 +4222,32 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4068,14 +4267,17 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4326,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4379,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4432,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4485,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,31 +4538,34 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -4368,14 +4585,17 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,31 +4614,32 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4438,14 +4659,17 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4718,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,31 +4771,34 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -4588,14 +4818,17 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,31 +4847,32 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4664,8 +4898,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +4951,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5004,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,31 +5057,34 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -4858,37 +5104,40 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4914,8 +5163,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4958,10 +5210,13 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>FOTB</t>
   </si>
@@ -656,146 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40816</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E8" s="3">
         <v>15600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>13000</v>
       </c>
       <c r="H8" s="3">
         <v>13000</v>
       </c>
       <c r="I8" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J8" s="3">
         <v>11800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9400</v>
-      </c>
-      <c r="R8" s="3">
-        <v>2700</v>
       </c>
       <c r="S8" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -847,35 +853,38 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E10" s="3">
         <v>15600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>13000</v>
       </c>
       <c r="H10" s="3">
         <v>13000</v>
       </c>
       <c r="I10" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J10" s="3">
         <v>11800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -900,8 +909,11 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -921,8 +933,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -974,8 +987,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1027,8 +1043,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1053,8 +1072,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1080,8 +1099,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1098,7 +1120,7 @@
         <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
@@ -1107,10 +1129,10 @@
         <v>500</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
+        <v>500</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
@@ -1127,14 +1149,17 @@
       <c r="Q15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1151,46 +1176,47 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E17" s="3">
         <v>7200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>7200</v>
       </c>
       <c r="J17" s="3">
         <v>7500</v>
       </c>
       <c r="K17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L17" s="3">
         <v>5600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1600</v>
       </c>
       <c r="P17" s="3">
         <v>1600</v>
@@ -1199,66 +1225,72 @@
         <v>1600</v>
       </c>
       <c r="R17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E18" s="3">
         <v>8400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5100</v>
       </c>
-      <c r="I18" s="3">
-        <v>4600</v>
-      </c>
       <c r="J18" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K18" s="3">
         <v>4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,88 +1310,92 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>500</v>
       </c>
       <c r="F20" s="3">
         <v>500</v>
       </c>
       <c r="G20" s="3">
+        <v>500</v>
+      </c>
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-7200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E21" s="3">
         <v>8200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1378,14 +1414,17 @@
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>1200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1410,8 +1449,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1437,61 +1476,67 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E23" s="3">
         <v>7900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,52 +1544,55 @@
         <v>2200</v>
       </c>
       <c r="E24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1400</v>
       </c>
       <c r="M24" s="3">
         <v>1400</v>
       </c>
       <c r="N24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1596,114 +1644,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1755,8 +1812,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1808,8 +1868,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1861,8 +1924,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1914,114 +1980,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-500</v>
       </c>
       <c r="F32" s="3">
         <v>-500</v>
       </c>
       <c r="G32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>7200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2073,119 +2148,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40816</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2205,8 +2289,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2226,61 +2311,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E41" s="3">
         <v>38800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>27500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43200</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J41" s="3">
+        <v>53700</v>
+      </c>
+      <c r="K41" s="3">
         <v>52500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2306,34 +2395,37 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>45200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>30600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>31500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>76600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>53500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2358,8 +2450,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2385,8 +2477,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2396,23 +2491,23 @@
       <c r="E44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3">
         <v>100</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="J44" s="3">
         <v>100</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2438,35 +2533,38 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E45" s="3">
         <v>28300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>59000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3">
+        <v>50200</v>
+      </c>
+      <c r="K45" s="3">
         <v>49300</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2491,35 +2589,38 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E46" s="3">
         <v>67000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>55900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>32900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>121000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J46" s="3">
+        <v>141600</v>
+      </c>
+      <c r="K46" s="3">
         <v>102100</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2544,35 +2645,38 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>186900</v>
+      </c>
+      <c r="E47" s="3">
         <v>184200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>172900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>167000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>165700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>145300</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J47" s="3">
+        <v>136800</v>
+      </c>
+      <c r="K47" s="3">
         <v>124200</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2597,61 +2701,67 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E48" s="3">
         <v>9400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3">
+        <v>14300</v>
+      </c>
+      <c r="K48" s="3">
         <v>14500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10400</v>
-      </c>
-      <c r="L48" s="3">
-        <v>14600</v>
       </c>
       <c r="M48" s="3">
         <v>14600</v>
       </c>
       <c r="N48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="O48" s="3">
         <v>14400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2665,11 +2775,11 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>8600</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -2677,11 +2787,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>2400</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2697,14 +2807,17 @@
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2756,8 +2869,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2809,34 +2925,37 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E52" s="3">
         <v>33400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>33100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2862,8 +2981,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2915,61 +3037,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1718100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1672400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1626200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1546300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1488900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1456800</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J54" s="3">
+        <v>1455100</v>
+      </c>
+      <c r="K54" s="3">
         <v>1353500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1354700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1265100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1161600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1077800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>993500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>958700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2989,8 +3117,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3010,35 +3139,36 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1513000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1481800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1437800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1354300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1235700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1244400</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3">
+        <v>1225100</v>
+      </c>
+      <c r="K57" s="3">
         <v>1101300</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -3063,8 +3193,11 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3078,11 +3211,11 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>102000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3116,8 +3249,11 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3142,8 +3278,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -3169,35 +3305,38 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1513000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1481800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1437800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1354300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1337700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1244400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J60" s="3">
+        <v>1225100</v>
+      </c>
+      <c r="K60" s="3">
         <v>1101300</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3222,61 +3361,67 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E61" s="3">
         <v>75500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>80500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>84500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>55300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>118500</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>139000</v>
+      </c>
+      <c r="K61" s="3">
         <v>161000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>189800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>181300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>91300</v>
-      </c>
-      <c r="N61" s="3">
-        <v>58500</v>
       </c>
       <c r="O61" s="3">
         <v>58500</v>
       </c>
       <c r="P61" s="3">
+        <v>58500</v>
+      </c>
+      <c r="Q61" s="3">
         <v>63500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3284,26 +3429,26 @@
         <v>12400</v>
       </c>
       <c r="E62" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F62" s="3">
         <v>13800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14200</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J62" s="3">
+        <v>12800</v>
+      </c>
+      <c r="K62" s="3">
         <v>14200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3328,8 +3473,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3381,8 +3529,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3434,8 +3585,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3487,61 +3641,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1612900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1569700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1532100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1455300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1402300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1377100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J66" s="3">
+        <v>1376900</v>
+      </c>
+      <c r="K66" s="3">
         <v>1276500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1283200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1196400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1095200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1013600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>931300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>900400</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3561,8 +3721,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3614,8 +3775,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3667,8 +3831,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3720,8 +3887,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3773,8 +3943,11 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3787,24 +3960,24 @@
       <c r="F72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3">
         <v>73300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>60200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3820,14 +3993,17 @@
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
+      <c r="R72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3879,8 +4055,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3932,8 +4111,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3985,61 +4167,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E76" s="3">
         <v>102700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>94200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>91000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>86600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>79700</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J76" s="3">
+        <v>78200</v>
+      </c>
+      <c r="K76" s="3">
         <v>77000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>68700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>66400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>64200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>62100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4091,119 +4279,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40816</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4223,8 +4420,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4249,8 +4447,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -4270,14 +4468,17 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4329,8 +4530,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4382,8 +4586,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4435,8 +4642,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4488,8 +4698,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4541,8 +4754,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4567,8 +4783,8 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -4588,14 +4804,17 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4615,8 +4834,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4641,8 +4861,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4662,14 +4882,17 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4721,8 +4944,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4774,8 +5000,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4800,8 +5029,8 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -4821,14 +5050,17 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4848,8 +5080,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4874,8 +5107,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4901,8 +5134,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4954,8 +5190,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5007,8 +5246,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5060,8 +5302,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5086,8 +5331,8 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -5107,14 +5352,17 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5139,8 +5387,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5166,31 +5414,34 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -5213,10 +5464,13 @@
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>FOTB</t>
   </si>
@@ -2542,7 +2542,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>27500</v>
+        <v>6000</v>
       </c>
       <c r="E45" s="3">
         <v>28300</v>
@@ -2554,7 +2554,7 @@
         <v>28200</v>
       </c>
       <c r="H45" s="3">
-        <v>4000</v>
+        <v>5600</v>
       </c>
       <c r="I45" s="3">
         <v>59000</v>
@@ -2598,7 +2598,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>57100</v>
+        <v>35500</v>
       </c>
       <c r="E46" s="3">
         <v>67000</v>
@@ -2610,7 +2610,7 @@
         <v>55900</v>
       </c>
       <c r="H46" s="3">
-        <v>32900</v>
+        <v>34500</v>
       </c>
       <c r="I46" s="3">
         <v>121000</v>
@@ -2654,7 +2654,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>186900</v>
+        <v>189900</v>
       </c>
       <c r="E47" s="3">
         <v>184200</v>
@@ -2766,7 +2766,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -2934,7 +2934,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>33700</v>
+        <v>43700</v>
       </c>
       <c r="E52" s="3">
         <v>33400</v>
@@ -2946,7 +2946,7 @@
         <v>32800</v>
       </c>
       <c r="H52" s="3">
-        <v>41200</v>
+        <v>39600</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -3202,7 +3202,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>36300</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1513000</v>
+        <v>1549200</v>
       </c>
       <c r="E60" s="3">
         <v>1481800</v>
@@ -3326,7 +3326,7 @@
         <v>1354300</v>
       </c>
       <c r="H60" s="3">
-        <v>1337700</v>
+        <v>1235700</v>
       </c>
       <c r="I60" s="3">
         <v>1244400</v>
@@ -3370,7 +3370,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>87500</v>
+        <v>54600</v>
       </c>
       <c r="E61" s="3">
         <v>75500</v>
@@ -3382,7 +3382,7 @@
         <v>84500</v>
       </c>
       <c r="H61" s="3">
-        <v>55300</v>
+        <v>157300</v>
       </c>
       <c r="I61" s="3">
         <v>118500</v>
@@ -3426,7 +3426,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12400</v>
+        <v>9100</v>
       </c>
       <c r="E62" s="3">
         <v>12400</v>
@@ -3951,8 +3951,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>90900</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="92">
   <si>
     <t>FOTB</t>
   </si>
@@ -656,152 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>40816</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>16900</v>
       </c>
-      <c r="E8" s="3">
-        <v>15600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>13300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>12800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>13000</v>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I8" s="3">
         <v>13000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>11800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9400</v>
-      </c>
-      <c r="S8" s="3">
-        <v>2700</v>
       </c>
       <c r="T8" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -856,38 +863,41 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
         <v>16900</v>
       </c>
-      <c r="E10" s="3">
-        <v>15600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>13300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>12800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>13000</v>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I10" s="3">
         <v>13000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>11800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -912,8 +922,11 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +947,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1004,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,8 +1063,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1075,8 +1095,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1102,40 +1122,43 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
-        <v>400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>500</v>
-      </c>
       <c r="J15" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
+        <v>500</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
@@ -1152,14 +1175,17 @@
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,49 +1203,50 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
         <v>8200</v>
       </c>
-      <c r="E17" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>7600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3">
         <v>5400</v>
       </c>
-      <c r="I17" s="3">
-        <v>7900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>7500</v>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="3">
         <v>7500</v>
       </c>
       <c r="L17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M17" s="3">
         <v>5600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1400</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1600</v>
       </c>
       <c r="Q17" s="3">
         <v>1600</v>
@@ -1228,69 +1255,75 @@
         <v>1600</v>
       </c>
       <c r="S17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
         <v>8700</v>
       </c>
-      <c r="E18" s="3">
-        <v>8400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>5700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>5300</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
         <v>7600</v>
       </c>
-      <c r="I18" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>4200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,94 +1344,98 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
-        <v>600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>500</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-7200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>8600</v>
       </c>
-      <c r="E21" s="3">
-        <v>8200</v>
-      </c>
       <c r="F21" s="3">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>6300</v>
       </c>
-      <c r="I21" s="3">
-        <v>5600</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>4600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1417,14 +1454,17 @@
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1452,8 +1492,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1479,120 +1519,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
         <v>8200</v>
       </c>
-      <c r="E23" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N23" s="3">
         <v>5200</v>
       </c>
-      <c r="G23" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>5900</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="O23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P23" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q23" s="3">
         <v>5100</v>
       </c>
-      <c r="J23" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="R23" s="3">
         <v>3700</v>
       </c>
-      <c r="M23" s="3">
-        <v>5200</v>
-      </c>
-      <c r="N23" s="3">
-        <v>5000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>2600</v>
-      </c>
-      <c r="P23" s="3">
-        <v>5100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>3700</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>2200</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E24" s="3">
         <v>2200</v>
       </c>
-      <c r="F24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
-      </c>
-      <c r="M24" s="3">
-        <v>1400</v>
       </c>
       <c r="N24" s="3">
         <v>1400</v>
       </c>
       <c r="O24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1696,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
         <v>6000</v>
       </c>
-      <c r="E26" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N26" s="3">
         <v>3800</v>
       </c>
-      <c r="G26" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="O26" s="3">
         <v>3700</v>
       </c>
-      <c r="J26" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="S26" s="3">
         <v>2800</v>
       </c>
-      <c r="M26" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>3700</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P26" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>2700</v>
-      </c>
-      <c r="R26" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
         <v>6000</v>
       </c>
-      <c r="E27" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="G27" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="O27" s="3">
         <v>3700</v>
       </c>
-      <c r="J27" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K27" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="S27" s="3">
         <v>2800</v>
       </c>
-      <c r="M27" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>3700</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>2700</v>
-      </c>
-      <c r="R27" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1873,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1932,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1991,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2050,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>7200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3">
         <v>6000</v>
       </c>
-      <c r="E33" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N33" s="3">
         <v>3800</v>
       </c>
-      <c r="G33" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="O33" s="3">
         <v>3700</v>
       </c>
-      <c r="J33" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="S33" s="3">
         <v>2800</v>
       </c>
-      <c r="M33" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N33" s="3">
-        <v>3700</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P33" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>2700</v>
-      </c>
-      <c r="R33" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2227,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3">
         <v>6000</v>
       </c>
-      <c r="E35" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N35" s="3">
         <v>3800</v>
       </c>
-      <c r="G35" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="O35" s="3">
         <v>3700</v>
       </c>
-      <c r="J35" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="S35" s="3">
         <v>2800</v>
       </c>
-      <c r="M35" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N35" s="3">
-        <v>3700</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P35" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>2700</v>
-      </c>
-      <c r="R35" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>40816</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2375,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,64 +2398,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3">
         <v>29600</v>
       </c>
-      <c r="E41" s="3">
-        <v>38800</v>
-      </c>
-      <c r="F41" s="3">
-        <v>42200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>27500</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3">
         <v>27600</v>
       </c>
-      <c r="I41" s="3">
-        <v>43200</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>53700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2398,34 +2488,37 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>45200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>30600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31500</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>76600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>53500</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2453,8 +2546,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2480,8 +2573,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2494,23 +2590,23 @@
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="3">
-        <v>100</v>
-      </c>
-      <c r="J44" s="3">
-        <v>100</v>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2536,38 +2632,41 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>6000</v>
       </c>
-      <c r="E45" s="3">
-        <v>28300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>31200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>28200</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>5600</v>
       </c>
-      <c r="I45" s="3">
-        <v>59000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>50200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49300</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2592,38 +2691,41 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3">
         <v>35500</v>
       </c>
-      <c r="E46" s="3">
-        <v>67000</v>
-      </c>
-      <c r="F46" s="3">
-        <v>73700</v>
-      </c>
-      <c r="G46" s="3">
-        <v>55900</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3">
         <v>34500</v>
       </c>
-      <c r="I46" s="3">
-        <v>121000</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>141600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>102100</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2648,38 +2750,41 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>189900</v>
       </c>
-      <c r="E47" s="3">
-        <v>184200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>172900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>167000</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>165700</v>
       </c>
-      <c r="I47" s="3">
-        <v>145300</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>136800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>124200</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2704,97 +2809,103 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
         <v>12800</v>
       </c>
-      <c r="E48" s="3">
-        <v>9400</v>
-      </c>
-      <c r="F48" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>13400</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>13800</v>
       </c>
-      <c r="I48" s="3">
-        <v>14100</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>14300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>14600</v>
       </c>
       <c r="N48" s="3">
         <v>14600</v>
       </c>
       <c r="O48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="P48" s="3">
         <v>14400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3">
         <v>8500</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3">
         <v>8600</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>2400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2810,14 +2921,17 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2986,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,37 +3045,40 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
         <v>43700</v>
       </c>
-      <c r="E52" s="3">
-        <v>33400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>33100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>32800</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
         <v>39600</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2984,8 +3104,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3163,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3">
         <v>1718100</v>
       </c>
-      <c r="E54" s="3">
-        <v>1672400</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1626200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1546300</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3">
         <v>1488900</v>
       </c>
-      <c r="I54" s="3">
-        <v>1456800</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>1455100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1353500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1354700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1265100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1161600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1077800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>993500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>958700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3247,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,38 +3270,39 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3">
         <v>1513000</v>
       </c>
-      <c r="E57" s="3">
-        <v>1481800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1437800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1354300</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
         <v>1235700</v>
       </c>
-      <c r="I57" s="3">
-        <v>1244400</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>1225100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1101300</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -3196,31 +3327,34 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3">
         <v>36300</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3252,8 +3386,11 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3281,8 +3418,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -3308,38 +3445,41 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3">
         <v>1549200</v>
       </c>
-      <c r="E60" s="3">
-        <v>1481800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1437800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1354300</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3">
         <v>1235700</v>
       </c>
-      <c r="I60" s="3">
-        <v>1244400</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
         <v>1225100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1101300</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3364,94 +3504,100 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>54600</v>
       </c>
-      <c r="E61" s="3">
-        <v>75500</v>
-      </c>
       <c r="F61" s="3">
-        <v>80500</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>84500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>157300</v>
       </c>
-      <c r="I61" s="3">
-        <v>118500</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>139000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>161000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>189800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>181300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>91300</v>
-      </c>
-      <c r="O61" s="3">
-        <v>58500</v>
       </c>
       <c r="P61" s="3">
         <v>58500</v>
       </c>
       <c r="Q61" s="3">
+        <v>58500</v>
+      </c>
+      <c r="R61" s="3">
         <v>63500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3">
         <v>9100</v>
       </c>
-      <c r="E62" s="3">
-        <v>12400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>13800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>16500</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3">
         <v>9300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
+        <v>12800</v>
+      </c>
+      <c r="L62" s="3">
         <v>14200</v>
       </c>
-      <c r="J62" s="3">
-        <v>12800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>14200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3476,8 +3622,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3681,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3740,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,64 +3799,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3">
         <v>1612900</v>
       </c>
-      <c r="E66" s="3">
-        <v>1569700</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1532100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1455300</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3">
         <v>1402300</v>
       </c>
-      <c r="I66" s="3">
-        <v>1377100</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>1376900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1276500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1283200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1196400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1095200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1013600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>931300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>900400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3883,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3940,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3999,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4058,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,41 +4117,44 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>90900</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3">
         <v>73300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>60200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3996,14 +4170,17 @@
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4235,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4294,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4353,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3">
         <v>105200</v>
       </c>
-      <c r="E76" s="3">
-        <v>102700</v>
-      </c>
-      <c r="F76" s="3">
-        <v>94200</v>
-      </c>
-      <c r="G76" s="3">
-        <v>91000</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3">
         <v>86600</v>
       </c>
-      <c r="I76" s="3">
-        <v>79700</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>78200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>77000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>68700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>66400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>64200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>62100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>58300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4471,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>40816</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>40724</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3">
         <v>6000</v>
       </c>
-      <c r="E81" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N81" s="3">
         <v>3800</v>
       </c>
-      <c r="G81" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="O81" s="3">
         <v>3700</v>
       </c>
-      <c r="J81" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="S81" s="3">
         <v>2800</v>
       </c>
-      <c r="M81" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N81" s="3">
-        <v>3700</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P81" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>2700</v>
-      </c>
-      <c r="R81" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,8 +4619,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4450,8 +4649,8 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4471,14 +4670,17 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4735,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4794,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4853,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4912,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,8 +4971,11 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4786,8 +5003,8 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -4807,14 +5024,17 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,8 +5055,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4864,8 +5085,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4885,14 +5106,17 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5171,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,8 +5230,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5032,8 +5262,8 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -5053,14 +5283,17 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5314,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5110,8 +5344,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5137,8 +5371,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5430,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5489,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,8 +5548,11 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5334,8 +5580,8 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -5355,14 +5601,17 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5390,8 +5639,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5417,8 +5666,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5443,8 +5695,8 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -5467,10 +5719,13 @@
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
